--- a/words_CZ/B1.5.xlsx
+++ b/words_CZ/B1.5.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PY_progs\Learn_CZ\words_CZ\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D19E1535-DA03-42F6-B47A-0A0579EC605F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,15 +24,786 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="253">
+  <si>
+    <t>(Ž) akciová společnost</t>
+  </si>
+  <si>
+    <t>акціонерне товариство</t>
+  </si>
+  <si>
+    <t>акционерное общество</t>
+  </si>
+  <si>
+    <t>joint-stock company</t>
+  </si>
+  <si>
+    <t>(Pl) bačkory</t>
+  </si>
+  <si>
+    <t>капці (кімнатні)</t>
+  </si>
+  <si>
+    <t>тапочки</t>
+  </si>
+  <si>
+    <t>slippers</t>
+  </si>
+  <si>
+    <t>bavlněný</t>
+  </si>
+  <si>
+    <t>бавовняний</t>
+  </si>
+  <si>
+    <t>хлопчатобумажный</t>
+  </si>
+  <si>
+    <t>cotton (adj)</t>
+  </si>
+  <si>
+    <t>(Pl) brýle</t>
+  </si>
+  <si>
+    <t>окуляри</t>
+  </si>
+  <si>
+    <t>очки</t>
+  </si>
+  <si>
+    <t>glasses</t>
+  </si>
+  <si>
+    <t>(M) deštník</t>
+  </si>
+  <si>
+    <t>парасолька</t>
+  </si>
+  <si>
+    <t>зонтик</t>
+  </si>
+  <si>
+    <t>umbrella</t>
+  </si>
+  <si>
+    <t>domácí</t>
+  </si>
+  <si>
+    <t>домашній</t>
+  </si>
+  <si>
+    <t>домашний</t>
+  </si>
+  <si>
+    <t>home, domestic</t>
+  </si>
+  <si>
+    <t>elegantní</t>
+  </si>
+  <si>
+    <t>елегантний</t>
+  </si>
+  <si>
+    <t>элегантный</t>
+  </si>
+  <si>
+    <t>elegant</t>
+  </si>
+  <si>
+    <t>expandovat</t>
+  </si>
+  <si>
+    <t>розширюватися</t>
+  </si>
+  <si>
+    <t>расширяться</t>
+  </si>
+  <si>
+    <t>to expand</t>
+  </si>
+  <si>
+    <t>fungovat</t>
+  </si>
+  <si>
+    <t>працювати (функціонувати)</t>
+  </si>
+  <si>
+    <t>работать (функционировать)</t>
+  </si>
+  <si>
+    <t>to work, to function</t>
+  </si>
+  <si>
+    <t>(Ž) halenka (blůza)</t>
+  </si>
+  <si>
+    <t>блузка</t>
+  </si>
+  <si>
+    <t>блузка (кофточка)</t>
+  </si>
+  <si>
+    <t>blouse</t>
+  </si>
+  <si>
+    <t>hedvábný</t>
+  </si>
+  <si>
+    <t>шовковий</t>
+  </si>
+  <si>
+    <t>шёлковый</t>
+  </si>
+  <si>
+    <t>silk (adj)</t>
+  </si>
+  <si>
+    <t>(Pl) jesle</t>
+  </si>
+  <si>
+    <t>ясла</t>
+  </si>
+  <si>
+    <t>ясли</t>
+  </si>
+  <si>
+    <t>nursery, crèche</t>
+  </si>
+  <si>
+    <t>(Pl) kabinky</t>
+  </si>
+  <si>
+    <t>примірочні</t>
+  </si>
+  <si>
+    <t>примерочные</t>
+  </si>
+  <si>
+    <t>changing rooms</t>
+  </si>
+  <si>
+    <t>(Pl) kalhotky</t>
+  </si>
+  <si>
+    <t>трусики (жіночі)</t>
+  </si>
+  <si>
+    <t>трусики</t>
+  </si>
+  <si>
+    <t>panties, knickers</t>
+  </si>
+  <si>
+    <t>(Pl) kalhoty</t>
+  </si>
+  <si>
+    <t>штани</t>
+  </si>
+  <si>
+    <t>брюки</t>
+  </si>
+  <si>
+    <t>trousers, pants</t>
+  </si>
+  <si>
+    <t>(M) klobouk</t>
+  </si>
+  <si>
+    <t>капелюх</t>
+  </si>
+  <si>
+    <t>шляпа</t>
+  </si>
+  <si>
+    <t>hat</t>
+  </si>
+  <si>
+    <t>(Ž) konfekce</t>
+  </si>
+  <si>
+    <t>готовий одяг</t>
+  </si>
+  <si>
+    <t>готовая одежда (конфекцион)</t>
+  </si>
+  <si>
+    <t>ready-made clothing</t>
+  </si>
+  <si>
+    <t>(Ž) košile s dlouhými rukávy</t>
+  </si>
+  <si>
+    <t>сорочка з довгими рукавами</t>
+  </si>
+  <si>
+    <t>рубашка с длинными рукавами</t>
+  </si>
+  <si>
+    <t>long-sleeved shirt</t>
+  </si>
+  <si>
+    <t>(Ž) košile s krátkými rukávy</t>
+  </si>
+  <si>
+    <t>сорочка з короткими рукавами</t>
+  </si>
+  <si>
+    <t>рубашка с короткими рукавами</t>
+  </si>
+  <si>
+    <t>short-sleeved shirt</t>
+  </si>
+  <si>
+    <t>kostkovaný</t>
+  </si>
+  <si>
+    <t>картатий (в клітинку)</t>
+  </si>
+  <si>
+    <t>в клеточку</t>
+  </si>
+  <si>
+    <t>checkered, plaid</t>
+  </si>
+  <si>
+    <t>kožený</t>
+  </si>
+  <si>
+    <t>шкіряний</t>
+  </si>
+  <si>
+    <t>кожаный</t>
+  </si>
+  <si>
+    <t>leather (adj)</t>
+  </si>
+  <si>
+    <t>(Pl) kraťasy (šortky)</t>
+  </si>
+  <si>
+    <t>шорти</t>
+  </si>
+  <si>
+    <t>шорты</t>
+  </si>
+  <si>
+    <t>shorts</t>
+  </si>
+  <si>
+    <t>(Ž) kravata</t>
+  </si>
+  <si>
+    <t>краватка</t>
+  </si>
+  <si>
+    <t>галстук</t>
+  </si>
+  <si>
+    <t>tie</t>
+  </si>
+  <si>
+    <t>(M) límeček</t>
+  </si>
+  <si>
+    <t>комірець</t>
+  </si>
+  <si>
+    <t>воротничок</t>
+  </si>
+  <si>
+    <t>collar</t>
+  </si>
+  <si>
+    <t>lněný</t>
+  </si>
+  <si>
+    <t>лляний</t>
+  </si>
+  <si>
+    <t>льняной</t>
+  </si>
+  <si>
+    <t>linen (adj)</t>
+  </si>
+  <si>
+    <t>(Pl) lodičky</t>
+  </si>
+  <si>
+    <t>туфлі-човники</t>
+  </si>
+  <si>
+    <t>туфли-лодочки</t>
+  </si>
+  <si>
+    <t>pumps, court shoes</t>
+  </si>
+  <si>
+    <t>(Ž) módní přehlídka</t>
+  </si>
+  <si>
+    <t>модний показ</t>
+  </si>
+  <si>
+    <t>модный показ</t>
+  </si>
+  <si>
+    <t>fashion show</t>
+  </si>
+  <si>
+    <t>(M) motýlek</t>
+  </si>
+  <si>
+    <t>метелик (краватка)</t>
+  </si>
+  <si>
+    <t>бабочка (галстук)</t>
+  </si>
+  <si>
+    <t>bow tie</t>
+  </si>
+  <si>
+    <t>(M) náhrdelník</t>
+  </si>
+  <si>
+    <t>намисто, кольє</t>
+  </si>
+  <si>
+    <t>ожерелье</t>
+  </si>
+  <si>
+    <t>necklace</t>
+  </si>
+  <si>
+    <t>(Pl) náušnice</t>
+  </si>
+  <si>
+    <t>сережки</t>
+  </si>
+  <si>
+    <t>серёжки</t>
+  </si>
+  <si>
+    <t>earrings</t>
+  </si>
+  <si>
+    <t>(M) návrhář</t>
+  </si>
+  <si>
+    <t>дизайнер, модельєр</t>
+  </si>
+  <si>
+    <t>модельер, дизайнер</t>
+  </si>
+  <si>
+    <t>designer</t>
+  </si>
+  <si>
+    <t>Nefunguje terminál.</t>
+  </si>
+  <si>
+    <t>Термінал не працює.</t>
+  </si>
+  <si>
+    <t>Терминал не работает.</t>
+  </si>
+  <si>
+    <t>The terminal is not working.</t>
+  </si>
+  <si>
+    <t>(Ž) noční košile</t>
+  </si>
+  <si>
+    <t>нічна сорочка</t>
+  </si>
+  <si>
+    <t>ночная сорочка</t>
+  </si>
+  <si>
+    <t>nightgown</t>
+  </si>
+  <si>
+    <t>nosit (oblečení)</t>
+  </si>
+  <si>
+    <t>носити (одяг)</t>
+  </si>
+  <si>
+    <t>носить (одежду)</t>
+  </si>
+  <si>
+    <t>to wear</t>
+  </si>
+  <si>
+    <t>(M) oblek</t>
+  </si>
+  <si>
+    <t>костюм (чоловічий)</t>
+  </si>
+  <si>
+    <t>костюм</t>
+  </si>
+  <si>
+    <t>suit</t>
+  </si>
+  <si>
+    <t>obsloužit zákazníka</t>
+  </si>
+  <si>
+    <t>обслужить клієнта</t>
+  </si>
+  <si>
+    <t>обслужить клиента</t>
+  </si>
+  <si>
+    <t>to serve a customer</t>
+  </si>
+  <si>
+    <t>odmítnout / odmítat</t>
+  </si>
+  <si>
+    <t>відмовити / відмовляти</t>
+  </si>
+  <si>
+    <t>отказаться / отказываться</t>
+  </si>
+  <si>
+    <t>to refuse, to reject</t>
+  </si>
+  <si>
+    <t>(Pl) plavky</t>
+  </si>
+  <si>
+    <t>купальник, плавки</t>
+  </si>
+  <si>
+    <t>swimsuit, swimwear</t>
+  </si>
+  <si>
+    <t>(Ž) podprsenka</t>
+  </si>
+  <si>
+    <t>бюстгальтер (ліфчик)</t>
+  </si>
+  <si>
+    <t>бюстгальтер (лифчик)</t>
+  </si>
+  <si>
+    <t>bra</t>
+  </si>
+  <si>
+    <t>(Pl) přírodní materiály</t>
+  </si>
+  <si>
+    <t>натуральні матеріали</t>
+  </si>
+  <si>
+    <t>натуральные материалы</t>
+  </si>
+  <si>
+    <t>natural materials</t>
+  </si>
+  <si>
+    <t>pruhovaný</t>
+  </si>
+  <si>
+    <t>смугастий</t>
+  </si>
+  <si>
+    <t>полосатый</t>
+  </si>
+  <si>
+    <t>striped</t>
+  </si>
+  <si>
+    <t>(Ž) punčocha</t>
+  </si>
+  <si>
+    <t>панчоха</t>
+  </si>
+  <si>
+    <t>чулок</t>
+  </si>
+  <si>
+    <t>stocking</t>
+  </si>
+  <si>
+    <t>(Pl) punčocháče</t>
+  </si>
+  <si>
+    <t>колготки</t>
+  </si>
+  <si>
+    <t>tights, pantyhose</t>
+  </si>
+  <si>
+    <t>puntíkovaný</t>
+  </si>
+  <si>
+    <t>у горошок</t>
+  </si>
+  <si>
+    <t>в горошек</t>
+  </si>
+  <si>
+    <t>polka-dotted</t>
+  </si>
+  <si>
+    <t>(M) rolák</t>
+  </si>
+  <si>
+    <t>водолазка, гольф</t>
+  </si>
+  <si>
+    <t>свитер с высоким воротом (водолазка)</t>
+  </si>
+  <si>
+    <t>turtleneck</t>
+  </si>
+  <si>
+    <t>(Pl) rukavice</t>
+  </si>
+  <si>
+    <t>рукавички</t>
+  </si>
+  <si>
+    <t>перчатки</t>
+  </si>
+  <si>
+    <t>gloves</t>
+  </si>
+  <si>
+    <t>(M) řetízek</t>
+  </si>
+  <si>
+    <t>ланцюжок</t>
+  </si>
+  <si>
+    <t>цепочка</t>
+  </si>
+  <si>
+    <t>chain (jewelry)</t>
+  </si>
+  <si>
+    <t>(Pl) slipy</t>
+  </si>
+  <si>
+    <t>труси (чоловічі плавки)</t>
+  </si>
+  <si>
+    <t>трусы (слипы)</t>
+  </si>
+  <si>
+    <t>briefs</t>
+  </si>
+  <si>
+    <t>spravit / spravovat oděv</t>
+  </si>
+  <si>
+    <t>полагодити / лагодити одяг</t>
+  </si>
+  <si>
+    <t>поправить / поправлять одежду</t>
+  </si>
+  <si>
+    <t>to mend / repair clothes</t>
+  </si>
+  <si>
+    <t>syntetický</t>
+  </si>
+  <si>
+    <t>синтетичний</t>
+  </si>
+  <si>
+    <t>синтетический</t>
+  </si>
+  <si>
+    <t>synthetic</t>
+  </si>
+  <si>
+    <t>(M) šátek</t>
+  </si>
+  <si>
+    <t>хустка</t>
+  </si>
+  <si>
+    <t>платок</t>
+  </si>
+  <si>
+    <t>scarf (head/neck)</t>
+  </si>
+  <si>
+    <t>(Ž) šála</t>
+  </si>
+  <si>
+    <t>шарф</t>
+  </si>
+  <si>
+    <t>шарф, шаль</t>
+  </si>
+  <si>
+    <t>scarf (winter)</t>
+  </si>
+  <si>
+    <t>(Pl) tenisky</t>
+  </si>
+  <si>
+    <t>кросівки, кеди</t>
+  </si>
+  <si>
+    <t>кроссовки</t>
+  </si>
+  <si>
+    <t>sneakers, trainers</t>
+  </si>
+  <si>
+    <t>(Pl) tepláky</t>
+  </si>
+  <si>
+    <t>спортивні штани</t>
+  </si>
+  <si>
+    <t>спортивные штаны</t>
+  </si>
+  <si>
+    <t>sweatpants, track bottoms</t>
+  </si>
+  <si>
+    <t>(S) tílko</t>
+  </si>
+  <si>
+    <t>майка</t>
+  </si>
+  <si>
+    <t>tank top, vest</t>
+  </si>
+  <si>
+    <t>(Ž) touha</t>
+  </si>
+  <si>
+    <t>бажання, жага</t>
+  </si>
+  <si>
+    <t>жажда, желание</t>
+  </si>
+  <si>
+    <t>desire, longing</t>
+  </si>
+  <si>
+    <t>(Pl) trenky</t>
+  </si>
+  <si>
+    <t>труси (сімейні)</t>
+  </si>
+  <si>
+    <t>трусы (семейные)</t>
+  </si>
+  <si>
+    <t>boxer shorts</t>
+  </si>
+  <si>
+    <t>vlněný</t>
+  </si>
+  <si>
+    <t>вовняний</t>
+  </si>
+  <si>
+    <t>шерстяной</t>
+  </si>
+  <si>
+    <t>woolen</t>
+  </si>
+  <si>
+    <t>vyzkoušet si sako</t>
+  </si>
+  <si>
+    <t>приміряти піджак</t>
+  </si>
+  <si>
+    <t>примерить пиджак</t>
+  </si>
+  <si>
+    <t>to try on a jacket</t>
+  </si>
+  <si>
+    <t>vyzkoušet si / zkusit si</t>
+  </si>
+  <si>
+    <t>приміряти (одяг)</t>
+  </si>
+  <si>
+    <t>примерить (одежду)</t>
+  </si>
+  <si>
+    <t>to try on (clothes)</t>
+  </si>
+  <si>
+    <t>zbankrotovat</t>
+  </si>
+  <si>
+    <t>збанкрутувати</t>
+  </si>
+  <si>
+    <t>обанкротиться</t>
+  </si>
+  <si>
+    <t>to go bankrupt</t>
+  </si>
+  <si>
+    <t>zlevnit</t>
+  </si>
+  <si>
+    <t>здешевити, знизити ціну</t>
+  </si>
+  <si>
+    <t>удешевить</t>
+  </si>
+  <si>
+    <t>to discount, to lower price</t>
+  </si>
+  <si>
+    <t>znárodnit</t>
+  </si>
+  <si>
+    <t>націоналізувати</t>
+  </si>
+  <si>
+    <t>национализировать</t>
+  </si>
+  <si>
+    <t>to nationalize</t>
+  </si>
+  <si>
+    <t>zvědavý</t>
+  </si>
+  <si>
+    <t>допитливий, цікавий</t>
+  </si>
+  <si>
+    <t>любопытный</t>
+  </si>
+  <si>
+    <t>curious</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +814,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,15 +822,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Звичайний" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +1128,907 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="65.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="27" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="52.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="39.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>